--- a/Outputs/Scenarios/PtX_demand_BE_Methanol.xlsx
+++ b/Outputs/Scenarios/PtX_demand_BE_Methanol.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.001354470379864105</v>
       </c>
       <c r="K16" t="n">
-        <v>0.008466705400423441</v>
+        <v>0.009498761543690178</v>
       </c>
     </row>
     <row r="17">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0141111756673724</v>
+        <v>0.01310651285373824</v>
       </c>
     </row>
     <row r="19">
@@ -1481,7 +1481,7 @@
         <v>1.951562544001469e-05</v>
       </c>
       <c r="K28" t="n">
-        <v>0.005644470266948961</v>
+        <v>0.005617076937316389</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.002005128495497259</v>
       </c>
       <c r="K30" t="n">
-        <v>0.0455901374767656</v>
+        <v>0.05114738545340099</v>
       </c>
     </row>
     <row r="31">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.07598356246127599</v>
+        <v>0.07057381762840571</v>
       </c>
     </row>
     <row r="33">
@@ -1999,7 +1999,7 @@
         <v>0.0001055330787103821</v>
       </c>
       <c r="K42" t="n">
-        <v>0.0303934249845104</v>
+        <v>0.03024592184074531</v>
       </c>
     </row>
     <row r="43">
